--- a/Analysis/Sensitivity_alpha_sweep_gemini.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_gemini.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.30468</v>
+        <v>0.30986</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32038</v>
+        <v>0.328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4722000000000001</v>
+        <v>0.48708</v>
       </c>
       <c r="I3" t="n">
-        <v>0.79366</v>
+        <v>0.79582</v>
       </c>
       <c r="J3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1788</v>
+        <v>0.17538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.17178</v>
+        <v>0.16924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.37848</v>
+        <v>0.37334</v>
       </c>
       <c r="I5" t="n">
         <v>0.69336</v>
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.29354</v>
+        <v>0.30368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.30418</v>
+        <v>0.31402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4669800000000001</v>
+        <v>0.47778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7832000000000001</v>
+        <v>0.7855000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.90974</v>
+        <v>0.91314</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9246000000000001</v>
+        <v>0.92716</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9210200000000001</v>
+        <v>0.92616</v>
       </c>
       <c r="I7" t="n">
         <v>0.9897</v>
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3082</v>
+        <v>0.31334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.32298</v>
+        <v>0.3306</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4774</v>
+        <v>0.49224</v>
       </c>
       <c r="I9" t="n">
-        <v>0.79366</v>
+        <v>0.79582</v>
       </c>
       <c r="J9" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.17606</v>
+        <v>0.17948</v>
       </c>
       <c r="G11" t="n">
-        <v>0.17334</v>
+        <v>0.17588</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36206</v>
+        <v>0.36716</v>
       </c>
       <c r="I11" t="n">
         <v>0.6974400000000001</v>
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.30468</v>
+        <v>0.31334</v>
       </c>
       <c r="G12" t="n">
-        <v>0.32038</v>
+        <v>0.3306</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4722000000000001</v>
+        <v>0.49224</v>
       </c>
       <c r="I12" t="n">
-        <v>0.79366</v>
+        <v>0.79582</v>
       </c>
       <c r="J12" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.9234399999999999</v>
+        <v>0.92684</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9348599999999999</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.93126</v>
+        <v>0.93642</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9846</v>
+        <v>0.9897</v>
       </c>
       <c r="J13" t="n">
         <v>195</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.17674</v>
+        <v>0.18016</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1733</v>
+        <v>0.1759</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36716</v>
+        <v>0.3723</v>
       </c>
       <c r="I14" t="n">
         <v>0.6974400000000001</v>
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.30122</v>
+        <v>0.30986</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3172</v>
+        <v>0.3254</v>
       </c>
       <c r="H15" t="n">
-        <v>0.46694</v>
+        <v>0.48708</v>
       </c>
       <c r="I15" t="n">
-        <v>0.79366</v>
+        <v>0.79582</v>
       </c>
       <c r="J15" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.91314</v>
+        <v>0.91654</v>
       </c>
       <c r="G16" t="n">
-        <v>0.92716</v>
+        <v>0.9323</v>
       </c>
       <c r="H16" t="n">
-        <v>0.92616</v>
+        <v>0.93126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9846</v>
+        <v>0.9897</v>
       </c>
       <c r="J16" t="n">
         <v>195</v>
